--- a/data_extactor/batch_10_fa/batch_0054_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0054_fa.xlsx
@@ -503,32 +503,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>نرم‌افزار برنامه‌ریزی کارکنان | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار Oracle | نرم‌افزار مدیریت روابط تجاری و مشتری SAP | نرم‌افزار زمان و حضور و غیاب</t>
+          <t>نرم‌افزار زمان‌بندی کارکنان | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Word | نرم‌افزار Oracle | نرم‌افزار مدیریت روابط تجاری و مشتری SAP | نرم‌افزار حضور و غیاب</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | مدیریت و امور اداری | خدمات مشتریان و پرسنل | پرسنل و منابع انسانی | قانون و دولت | زبان انگلیسی | اداری | آموزش و تربیت | رایانه‌ها و الکترونیک | روان‌شناسی | مخابرات | مهندسی و فناوری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | قانون و دولت | زبان انگلیسی | اداری | آموزش و پرورش | رایانه و الکترونیک | روان‌شناسی | مخابرات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | بینایی دور | تشخیص گفتار | استدلال قیاسی | درک کتبی | بیان کتبی | انعطاف‌پذیری بستار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | سرعت بستار | سرعت ادراکی | روان بودن ایده‌ها | انعطاف‌پذیری مقوله‌ای</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | بینایی دور | تشخیص گفتار | استدلال قیاسی | درک کتبی | بیان کتبی | انعطاف‌پذیری بستار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | سرعت بستار | سرعت ادراکی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>تماس با دیگران | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | اهمیت دقیق یا منظم بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان | فضای باز، در معرض همه شرایط آب و هوایی | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | نامه‌ها و یادداشت‌های کتبی</t>
+          <t>ارتباط با دیگران | مکالمات تلفنی | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | موقعیت‌های تعارض | نزدیکی فیزیکی | اهمیت تکرار وظایف یکسان | فضای باز، در معرض تمام شرایط آب و هوایی | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول کارکنان سرگرمی و تفریحی، به جز خدمات قمار | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | سرپرستان خط اول دستیاران، کارگران و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارکنان خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصب‌کنندگان و تعمیرکاران | سرپرستان خط اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان پشتیبانی اداری و دفتری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارکنان خدمات شخصی | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان تولید و عملیات | افسران گشت پلیس و کلانتر | متخصصان پیشگیری از خسارت خرده‌فروشی | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیت | پلیس ترانزیت و راه‌آهن</t>
+          <t>مدیران خدمات اداری | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول کارگران سرگرمی و تفریح، به جز خدمات قمار | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کمک‌یارها، کارگران ساده و جابجا‌کنندگان دستی مواد | سرپرستان خط اول کارگران خانه‌داری و سرایداری | سرپرستان خط اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابجایی مواد | سرپرستان خط اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده اول کارکنان فروش غیرخرده‌فروشی | سرپرستان خط اول کارکنان دفتری و پشتیبانی اداری | سرپرستان خط اول مهمانداران مسافری | سرپرستان خط اول کارگران خدمات شخصی | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان رده اول کارگران تولید و بهره‌برداری | ماموران گشت پلیس و کلانتر | متخصصان پیشگیری از خسارت خرده‌فروشی | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیتی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | نرم‌افزار برنامه‌ریزی</t>
+          <t>Microsoft Excel | Microsoft Word | Microsoft PowerPoint | Microsoft Outlook | نرم‌افزار Microsoft Office | نرم‌افزار ایمیل | Microsoft Access | Microsoft SharePoint | نرم‌افزار مرورگر وب | نرم‌افزار پایگاه داده | Google Docs | نرم‌افزار مدیریت تقویم | برنامه‌های صفحه‌گسترده | Adobe Acrobat | نرم‌افزار زمان‌بندی</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | مدیریت و امور اداری | خدمات مشتریان و پرسنل | قانون و دولت | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و تربیت | روان‌شناسی | رایانه‌ها و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری مقوله‌ای | روان بودن ایده‌ها | اصالت | توجه انتخابی | تقسیم زمان | تجسم | حفظ کردن</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | تماس با دیگران | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | مکالمات تلفنی | پیامد خطا | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | صرف زمان به صورت ایستاده | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض شرایط خطرناک | فضای باز، در معرض همه شرایط آب و هوایی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | فشار زمانی | ایمیل | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | تعامل با مشتریان خارجی یا عموم مردم | مکالمات تلفنی | پیامد خطا | فراوانی تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | نزدیکی فیزیکی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | صرف زمان برای ایستادن | صرف زمان برای راه رفتن یا دویدن | قرار گرفتن در معرض شرایط خطرناک | فضای باز، در معرض تمام شرایط آب و هوایی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | فشار زمانی | ایمیل | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | سخنرانی عمومی | موقعیت‌های تعارض | سطح رقابت | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان خط اول کارکنان امنیتی | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | نگهبانان امنیتی | متخصصان پیشگیری از خسارت خرده‌فروشی | افسران نظارت بر قمار و بازرسان قمار | کارآگاهان و بازرسان خصوصی | غربالگران امنیت حمل و نقل | افسران اصلاح و تربیت و زندانبانان | افسران گشت پلیس و کلانتر | کارآگاهان و بازرسان جنایی | کارکنان خدمات حفاظتی، همه موارد دیگر | مدیران امنیت | مدیران مدیریت بحران | افسران انطباق | متخصصان بهداشت و ایمنی شغلی | مدیران پیشگیری از خسارت | مدیران عمومی و عملیاتی | متخصصان مدیریت امنیت</t>
+          <t>سرپرستان خط اول کارکنان امنیتی | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول آتش‌نشانی و پیشگیری | نگهبانان امنیتی | متخصصان پیشگیری از خسارت خرده‌فروشی | ماموران نظارت بر قمار و بازرسان قمار | کارآگاهان و بازرسان خصوصی | غربالگران امنیتی حمل و نقل | افسران اصلاح و تربیت و زندانبانان | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان جنایی | کارکنان خدمات حفاظتی، سایر | مدیران امنیتی | مدیران مدیریت بحران | افسران انطباق | متخصصان بهداشت و ایمنی شغلی | مدیران پیشگیری از زیان | مدیران عمومی و عملیات | متخصصان مدیریت امنیت</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | خدمات مشتریان و پرسنل | آموزش و تربیت | ساختمان و ساخت و ساز | زبان انگلیسی | مکانیک | پزشکی و دندانپزشکی | مخابرات | مدیریت و امور اداری | حمل و نقل | قانون و دولت | شیمی | روان‌شناسی | ریاضیات</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | ساختمان و ساخت‌وساز | زبان انگلیسی | مکانیک | پزشکی و دندان‌پزشکی | مخابرات | مدیریت و اداره | حمل و نقل | قانون و دولت | شیمی | روان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | ثبات دست و بازو | قدرت ایستا | بینایی دور | استقامت | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | دقت کنترل | هماهنگی چند عضوی | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | قدرت تنه | قدرت پویا | زمان واکنش | چالاکی دستی | تشخیص گفتار | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری دامنه حرکت | درک کتبی | جهت‌یابی فضایی | تجسم | درک عمق | تشخیص رنگ‌های بصری | قدرت انفجاری | توجه انتخابی | سرعت بستار | انعطاف‌پذیری مقوله‌ای | هماهنگی کلی بدن | بیان کتبی | تعادل کلی بدن | جهت‌گیری پاسخ | چالاکی انگشتان</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | ثبات دست و بازو | قدرت ایستا | بینایی دور | استقامت | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | دقت کنترل | هماهنگی چند عضو | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | قدرت تنه | قدرت پویا | زمان عکس‌العمل | مهارت دستی | تشخیص گفتار | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری دامنه حرکت | درک کتبی | جهت‌گیری فضایی | تجسم | درک عمق | تشخیص رنگ بصری | قدرت انفجاری | توجه انتخابی | سرعت بستار | انعطاف‌پذیری دسته‌بندی | هماهنگی کلی بدن | بیان کتبی | تعادل کلی بدن | جهت‌گیری پاسخ | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی, عینک, دستکش, محافظ گوش, کلاه ایمنی یا جلیقه نجات | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | فضای باز، در معرض همه شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا منظم بودن | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | مکالمات تلفنی | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض بیماری یا عفونت‌ها | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفسی، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | داخل ساختمان، بدون کنترل محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های نامناسب | سطح رقابت | فشار زمانی | قرار گرفتن در معرض مکان‌های مرتفع | برخورد با افراد ناراحت، عصبانی یا بی‌ادب</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | نزدیکی فیزیکی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعامل با مشتریان خارجی یا عموم مردم | فضای باز، در معرض تمام شرایط آب و هوایی | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض آلاینده‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | مکالمات تلفنی | پیامد خطا | قرار گرفتن در معرض تجهیزات خطرناک | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | پیامدهای کاری و نتایج سایر کارکنان | ایمیل | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی تخصصی مانند دستگاه تنفس، هارنس ایمنی، لباس‌های محافظ کامل یا محافظت در برابر تشعشع | قرار گرفتن در معرض شرایط خطرناک | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | قرار گرفتن در معرض فضای کاری تنگ، موقعیت‌های بدنی نامناسب | سطح رقابت | فشار زمانی | قرار گرفتن در معرض ارتفاعات بالا | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رانندگان و خدمه آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | نصب‌کنندگان و تعمیرکاران خطوط برق | مدیران مدیریت بحران | تکنسین‌های فوریت‌های پزشکی | بازرسان و محققان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | کارگران حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | پیراپزشکان | ملوانان و روغن‌کاران دریایی | نگهبانان امنیتی | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
+          <t>رانندگان و متصدیان آمبولانس، به جز تکنسین‌های فوریت‌های پزشکی | نصابان و تعمیرکاران خطوط انتقال نیروی برق | مدیران مدیریت بحران | تکنسین‌های فوریت‌های پزشکی | بازرسان و محققان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش‌سوزی | سرپرستان خط اول آتش‌نشانی و پیشگیری | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | کارگران حذف مواد خطرناک | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | پارامدیک‌ها | ملوانان و روغن‌کاران دریایی | نگهبانان امنیتی | مهندسان کشتی | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,27 +679,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | خدمات مشتریان و پرسنل | ساختمان و ساخت و ساز | قانون و دولت | آموزش و تربیت | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | قانون و دولت | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | انعطاف‌پذیری مقوله‌ای | وضوح گفتار | تشخیص گفتار | توجه انتخابی | روان بودن ایده‌ها | تشخیص رنگ‌های بصری | بینایی دور | اصالت</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | روانی ایده‌ها | تشخیص رنگ بصری | بینایی دور | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | مکالمات تلفنی | تماس با دیگران | ایمیل | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا منظم بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | فضای باز، در معرض همه شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | داخل ساختمان، کنترل محیطی | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | داخل ساختمان، بدون کنترل محیطی | نزدیکی فیزیکی</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | ارتباط با دیگران | ایمیل | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تعامل با مشتریان خارجی یا عموم مردم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | فراوانی تصمیم‌گیری | فضای باز، در معرض تمام شرایط آب و هوایی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | نامه‌ها و یادداشت‌های کتبی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | محیط داخلی، بدون کنترل شرایط محیطی | نزدیکی فیزیکی</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازرسان هوانوردی | بازرسان ساختمان و ساخت و ساز | مدیران مدیریت بحران | بازرسان انطباق محیطی | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | مهندسان پیشگیری و حفاظت از آتش | آتش‌نشانان | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | سرپرستان خط اول کارکنان امنیتی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیت | نصب‌کنندگان سیستم‌های امنیتی و هشدار آتش | پلیس ترانزیت و راه‌آهن | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>بازرسان هوانوردی | بازرسان ساختمان و ساخت‌وساز | مدیران مدیریت بحران | بازرسان انطباق زیست‌محیطی | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | مهندسان پیشگیری و حفاظت از آتش‌سوزی | آتش‌نشانان | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول کارکنان امنیتی | بازرسان و متخصصان پیشگیری از آتش‌سوزی جنگل | بازرسان و محققان اموال دولتی | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | نگهبانان امنیتی | متخصصان مدیریت امنیت | مدیران امنیتی | نصب‌کنندگان سیستم‌های دزدگیر و اعلام حریق | پلیس ترانزیت و راه‌آهن | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,27 +736,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | استراتژی‌های یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و پرسنل | آموزش و تربیت | پرسنل و منابع انسانی | امنیت و ایمنی عمومی | قانون و دولت | رایانه‌ها و الکترونیک | زبان انگلیسی | حمل و نقل | اداری | مکانیک | ارتباطات و رسانه | جغرافیا</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | قانون و دولت | رایانه و الکترونیک | زبان انگلیسی | حمل و نقل | اداری | مکانیک | ارتباطات و رسانه | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | بینایی دور | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار | سرعت ادراکی | بیان کتبی | سرعت بستار | ترتیب‌دهی اطلاعات | تشخیص گفتار | درک عمق | هماهنگی چند عضوی | توجه انتخابی | انعطاف‌پذیری مقوله‌ای | اصالت</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | بینایی دور | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار | سرعت ادراکی | بیان کتبی | سرعت بستار | ترتیب‌دهی اطلاعات | تشخیص گفتار | درک عمق | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | تماس با دیگران | مکالمات تلفنی | ایمیل | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | فضای باز، در معرض همه شرایط آب و هوایی | آزادی در تصمیم‌گیری | داخل ساختمان، بدون کنترل محیطی | سلامت و ایمنی سایر کارکنان | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا منظم بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | پیامد خطا | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، نیش‌ها یا گزیدگی‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک</t>
+          <t>تأثیر تصمیمات بر همکاران یا نتایج شرکت | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | مکالمات تلفنی | ایمیل | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | فضای باز، در معرض تمام شرایط آب و هوایی | آزادی در تصمیم‌گیری | محیط داخلی، بدون کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | تعامل با مشتریان خارجی یا عموم مردم | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | فراوانی تصمیم‌گیری | قرار گرفتن در معرض آلاینده‌ها | تعیین وظایف، اولویت‌ها و اهداف | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | پیامدهای کاری و نتایج سایر کارکنان | اهمیت دقیق یا درست بودن | قرار گرفتن در معرض دماهای بسیار گرم یا سرد | فشار زمانی | پیامد خطا | قرار گرفتن در معرض سوختگی‌های جزئی، بریدگی‌ها، گاز گرفتگی‌ها یا نیش‌ها | قرار گرفتن در معرض شرایط نوری بسیار روشن یا ناکافی | اهمیت تکرار وظایف یکسان | قرار گرفتن در معرض تجهیزات خطرناک</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران مدیریت بحران | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | دانشمندان و متخصصان محیط زیست، از جمله بهداشت | بازرسان و محققان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش | آتش‌نشانان | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | دیسپچرهای امنیت عمومی | مدیران مرتع | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل و نقل، به جز هوانوردی</t>
+          <t>مدیران مدیریت بحران | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | دانشمندان و متخصصان محیط زیست، شامل بهداشت | بازرسان و محققان آتش‌نشانی | مهندسان پیشگیری و حفاظت از آتش‌سوزی | آتش‌نشانان | سرپرستان خط اول کارکنان کشاورزی، ماهیگیری و جنگل‌داری | سرپرستان خط اول آتش‌نشانی و پیشگیری | تکنسین‌های جنگل و حفاظت | کارگران جنگل و حفاظت | جنگل‌بانان | مهندسان بهداشت و ایمنی، به جز مهندسان و بازرسان ایمنی معدن | نجات‌غریق‌ها، گشت اسکی و سایر کارکنان خدمات حفاظتی تفریحی | متخصصان بهداشت و ایمنی شغلی | تکنسین‌های بهداشت و ایمنی شغلی | اپراتورهای مخابراتی امنیت عمومی | مدیران مراتع | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به جز هوانوردی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتریان و پرسنل | روان‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -808,12 +808,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | داخل ساختمان، کنترل محیطی | اهمیت دقیق یا منظم بودن | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | مکالمات تلفنی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | ایمیل</t>
+          <t>ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | نزدیکی فیزیکی | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | مکالمات تلفنی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | ایمیل</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و افسران دادرسی | داوران، میانجی‌ها و مصالحه‌دهندگان | پزشکان قانونی | افسران اصلاح و تربیت و زندانبانان | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | منشی‌های دادگاه، شهرداری و مجوز | افسران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | قضات، قضات دادگاه و دادرسان | دستیاران قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | افسران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران تعلیق و متخصصان درمان اصلاحی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | داوران، میانجی‌گران و مصالحه‌گران | بازرسان مرگ | افسران اصلاح و تربیت و زندانبانان | گزارشگران دادگاه و زیرنویس‌نویسان همزمان | کارمندان دادگاه، شهرداری و مجوز | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | قضات، قضات دادگاه‌های بدوی و قضات صلح | کارمندان حقوقی قضایی | وکلا | منشی‌های حقوقی و دستیاران اداری | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران مشروط و متخصصان درمان اصلاحی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,27 +850,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | استراتژی‌های یادگیری | نگارش</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>امنیت و ایمنی عمومی | زبان انگلیسی | قانون و دولت | خدمات مشتریان و پرسنل | مدیریت و امور اداری | رایانه‌ها و الکترونیک | روان‌شناسی | آموزش و تربیت | اداری | مخابرات</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | رایانه و الکترونیک | روان‌شناسی | آموزش و پرورش | اداری | مخابرات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | توجه انتخابی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی دور | استقامت | بیان کتبی | قدرت تنه | قدرت پویا | قدرت انفجاری | قدرت ایستا | زمان واکنش | هماهنگی چند عضوی | چالاکی دستی | ثبات دست و بازو | تقسیم زمان | سرعت ادراکی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | توجه انتخابی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی دور | استقامت | بیان کتبی | قدرت تنه | قدرت پویا | قدرت انفجاری | قدرت ایستا | زمان عکس‌العمل | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | تقسیم توجه | سرعت ادراکی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>گفتگوهای چهره به چهره با افراد و درون تیم‌ها | مکالمات تلفنی | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | تماس با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا منظم بودن | ایمیل | داخل ساختمان، کنترل محیطی | فشار زمانی | موقعیت‌های تعارض | سلامت و ایمنی سایر کارکنان | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویز مزاحم یا ناراحت‌کننده | قرار گرفتن در معرض بیماری یا عفونت‌ها | پوشیدن تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | فشار زمانی | موقعیت‌های تعارض | سلامت و ایمنی سایر کارکنان | برخورد با افراد خشن یا از نظر فیزیکی پرخاشگر | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | اهمیت تکرار وظایف یکسان | آزادی در تصمیم‌گیری | تعامل با مشتریان خارجی یا عموم مردم | نزدیکی فیزیکی | قرار گرفتن در معرض صداها و سطوح نویزی که حواس‌پرت‌کننده یا آزاردهنده هستند | قرار گرفتن در معرض بیماری‌ها یا عفونت‌ها | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | نامه‌ها و یادداشت‌های کتبی | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامدهای کاری و نتایج سایر کارکنان | پیامد خطا | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>ضابطان دادگستری | مددکاران اجتماعی کودک، خانواده و مدرسه | پزشکان قانونی | منشی‌های دادگاه، شهرداری و مجوز | معلمان عدالت کیفری و اجرای قانون، پس از دبیرستان | کارآگاهان و بازرسان جنایی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول کارکنان آتش‌نشانی و پیشگیری | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | مدیران خدمات پزشکی و بهداشتی | افسران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران تعلیق و متخصصان درمان اصلاحی | دستیاران روان‌پزشکی | مشاوران توانبخشی | مشاوران اقامتی | نگهبانان امنیتی | مدیران خدمات اجتماعی و جامعه | پلیس ترانزیت و راه‌آهن</t>
+          <t>ضابطان دادگستری | مددکاران اجتماعی کودک، خانواده و مدرسه | بازرسان مرگ | کارمندان دادگاه، شهرداری و مجوز | مدرسان عدالت کیفری و اجرای قانون، آموزش عالی | کارآگاهان و بازرسان جنایی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول آتش‌نشانی و پیشگیری | سرپرستان خط اول پلیس و کارآگاهان | سرپرستان خط اول کارکنان امنیتی | مدیران خدمات پزشکی و بهداشتی | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران مشروط و متخصصان درمان اصلاحی | کمک‌یاران روان‌پزشکی | مشاوران توانبخشی | مشاوران خوابگاه و اقامتگاه | نگهبانان امنیتی | مدیران خدمات اجتماعی و جامعه | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AccessData FTK | Adobe Photoshop | نرم‌افزار مدیریت پرونده | نرم‌افزار طراحی چهره‌نگاری رایانه‌ای | Corel WordPerfect Office Suite | نرم‌افزار نقشه‌برداری جرم | DataWorks Plus Digital CrimeScene | DeChant Consulting Services iWitness | DesignWare 3D EyeWitness | Digital Image Management Solutions Crime Scene | ESRI ArcView | نرم‌افزار ایمیل | Eos Systems PhotoModeler | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار گرافیک | Guidance Software EnCase Enterprise | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | پایگاه‌های داده اطلاعات اجرای قانون | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Visio | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی اطلاعات بالستیک یکپارچه NIBIN | SAS | SmartDraw Legal | زبان پرس‌و‌جوی ساختاریافته SQL | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | نرم‌افزار مرورگر وب</t>
+          <t>AccessData FTK | Adobe Photoshop | نرم‌افزار مدیریت پرونده | نرم‌افزار طراحی چهره‌نگاری رایانه‌ای | Corel WordPerfect Office Suite | نرم‌افزار نقشه‌برداری جرم | DataWorks Plus Digital CrimeScene | DeChant Consulting Services iWitness | DesignWare 3D EyeWitness | Digital Image Management Solutions Crime Scene | ESRI ArcView | نرم‌افزار ایمیل | Eos Systems PhotoModeler | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار گرافیکی | Guidance Software EnCase Enterprise | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | پایگاه‌های داده اطلاعات اجرای قانون | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Publisher | Microsoft Visio | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی یکپارچه اطلاعات بالستیک NIBIN | SAS | SmartDraw Legal | زبان پرس‌وجوی ساختاریافته SQL | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>قانون و دولت | امنیت و ایمنی عمومی | زبان انگلیسی | خدمات مشتریان و پرسنل | روان‌شناسی | رایانه‌ها و الکترونیک | آموزش و تربیت | اداری | مدیریت و امور اداری | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش | اداری | مدیریت و اداره | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری مقوله‌ای | انعطاف‌پذیری بستار | بینایی دور | سرعت بستار | روان بودن ایده‌ها | سرعت ادراکی | توجه انتخابی | تقسیم زمان | اصالت</t>
+          <t>درک شفاهی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | بینایی دور | سرعت بستار | روانی ایده‌ها | سرعت ادراکی | توجه انتخابی | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>مکالمات تلفنی | ایمیل | برخورد با مشتریان خارجی یا عموم مردم به طور کلی | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | تماس با دیگران | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | تأثیر تصمیمات بر همکاران یا نتایج شرکت | داخل ساختمان, کنترل محیطی | اهمیت دقیق یا منظم بودن | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | پیامد خطا | موقعیت‌های تعارض | برخورد با افراد ناراحت، عصبانی یا بی‌ادب | فضای باز، در معرض همه شرایط آب و هوایی | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | اهمیت تکرار وظایف یکسان | فشار زمانی | نزدیکی فیزیکی | داخل ساختمان، بدون کنترل محیطی | صرف زمان به صورت نشسته</t>
+          <t>مکالمات تلفنی | ایمیل | تعامل با مشتریان خارجی یا عموم مردم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | تأثیر تصمیمات بر همکاران یا نتایج شرکت | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | فراوانی تصمیم‌گیری | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | پیامد خطا | موقعیت‌های تعارض | برخورد با افراد ناخوشایند، عصبانی یا بی‌ادب | فضای باز، در معرض تمام شرایط آب و هوایی | نامه‌ها و یادداشت‌های کتبی | سلامت و ایمنی سایر کارکنان | اهمیت تکرار وظایف یکسان | فشار زمانی | نزدیکی فیزیکی | محیط داخلی، بدون کنترل شرایط محیطی | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>قضات حقوق اداری، داوران و افسران دادرسی | ضابطان دادگستری | افسران انطباق | پزشکان قانونی | افسران اصلاح و تربیت و زندانبانان | افسران گمرک و حفاظت مرزی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول پلیس و کارآگاهان | تکنسین‌های علوم جنایی | ارزیابان، بازرسان و تحلیلگران تقلب | تحلیلگران اطلاعاتی | دستیاران قضایی | وکلا | افسران شناسایی و سوابق پلیس | افسران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران تعلیق و متخصصان درمان اصلاحی | متخصصان پیشگیری از خسارت خرده‌فروشی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
+          <t>قضات حقوق اداری، داوران و مسئولان رسیدگی | ضابطان دادگستری | افسران انطباق | بازرسان مرگ | افسران اصلاح و تربیت و زندانبانان | ماموران گمرک و حفاظت مرزی | سرپرستان خط اول افسران اصلاح و تربیت | سرپرستان خط اول پلیس و کارآگاهان | تکنسین‌های علوم قانونی | بازرسان، محققان و تحلیلگران کلاهبرداری | تحلیلگران اطلاعاتی | کارمندان حقوقی قضایی | وکلا | افسران شناسایی و سوابق پلیس | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | افسران مشروط و متخصصان درمان اصلاحی | متخصصان پیشگیری از خسارت خرده‌فروشی | نگهبانان امنیتی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Adobe Photoshop | نرم‌افزار طراحی چهره‌نگاری رایانه‌ای | DataWorks Plus Digital CrimeScene | نرم‌افزار پایگاه داده | DeChant Consulting Services iWitness | DesignWare 3D EyeWitness | Digital Image Management Solutions Crime Scene | Eos Systems PhotoModeler | نرم‌افزار بهبود تصویر | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی اطلاعات بالستیک یکپارچه NIBIN | SmartDraw Legal | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | نرم‌افزار مرورگر وب</t>
+          <t>Adobe Photoshop | نرم‌افزار طراحی چهره‌نگاری رایانه‌ای | DataWorks Plus Digital CrimeScene | نرم‌افزار پایگاه داده | DeChant Consulting Services iWitness | DesignWare 3D EyeWitness | Digital Image Management Solutions Crime Scene | Eos Systems PhotoModeler | نرم‌افزار بهبود تصویر | سیستم یکپارچه خودکار شناسایی اثر انگشت IAFIS | Linux | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Visio | Microsoft Windows | Microsoft Word | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | شبکه ملی یکپارچه اطلاعات بالستیک NIBIN | SmartDraw Legal | The CAD Zone The Crime Zone | Trancite Logic Systems ScenePD | Visual Statement Vista FX3 CSI | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -969,22 +969,22 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>قانون و دولت | اداری | زبان انگلیسی | امنیت و ایمنی عمومی | رایانه‌ها و الکترونیک | خدمات مشتریان و پرسنل | آموزش و تربیت</t>
+          <t>قانون و دولت | اداری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | حساسیت به مسئله | انعطاف‌پذیری مقوله‌ای | ثبات دست و بازو | روان بودن ایده‌ها | توجه انتخابی | سرعت ادراکی | تشخیص رنگ‌های بصری | بینایی دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ثبات دست و بازو | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | تشخیص رنگ بصری | بینایی دور</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا منظم بودن | آزادی در تصمیم‌گیری | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | داخل ساختمان، کنترل محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه سرپوشیده یا کار با تجهیزات سرپوشیده | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | تماس با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان به صورت نشسته | نزدیکی فیزیکی | فضای باز، در معرض همه شرایط آب و هوایی</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | آزادی در تصمیم‌گیری | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | در یک وسیله نقلیه محصور یا کار با تجهیزات محصور | کار با یا مشارکت در یک گروه کاری یا تیم | فراوانی تصمیم‌گیری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | نزدیکی فیزیکی | فضای باز، در معرض تمام شرایط آب و هوایی</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>هماهنگ‌کنندگان تحقیقات بالینی | افسران انطباق | پزشکان قانونی | کارآگاهان و بازرسان جنایی | تحلیلگران جرم‌شناسی دیجیتال | بازرسان انطباق محیطی | تکنسین‌های علوم و حفاظت محیط زیست، از جمله بهداشت | بایگانان پرونده | سرپرستان خط اول پلیس و کارآگاهان | تکنسین‌های علوم جنایی | ارزیابان، بازرسان و تحلیلگران تقلب | بازرسان و محققان اموال دولتی | تحلیلگران اطلاعاتی | تکنسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | دستیاران حقوقی و وکلا | افسران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | دستیاران پژوهشی علوم اجتماعی | دستیاران آماری</t>
+          <t>هماهنگ‌کنندگان تحقیقات بالینی | افسران انطباق | بازرسان مرگ | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌شناسی دیجیتال | بازرسان انطباق زیست‌محیطی | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | کارمندان بایگانی | سرپرستان خط اول پلیس و کارآگاهان | تکنسین‌های علوم قانونی | بازرسان، محققان و تحلیلگران کلاهبرداری | بازرسان و محققان اموال دولتی | تحلیلگران اطلاعاتی | تکنیسین‌های آزمایشگاه پزشکی و بالینی | تکنولوژیست‌های آزمایشگاه پزشکی و بالینی | پارالیگال‌ها و دستیاران حقوقی | ماموران گشت پلیس و کلانتر | کارآگاهان و بازرسان خصوصی | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,32 +1016,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Amazon Simple Storage Service S3 | نرم‌افزار Amazon Web Services AWS | Apache Hadoop | Apache Hive | Apache Kafka | Apache Pig | Apache Spark | Arrival Departure Information System ADIS | Automated Targeting System ATS | Bing | Biometric Storage System BSS | C++ | نرم‌افزار چت‌بات | Computer Linked Application Information Management System CLAIMS | Consular Consolidated Database CCD | نرم‌افزار تجسم داده‌ها | Django | نرم‌افزار ESRI ArcGIS | ESRI ArcView | نرم‌افزار ایمیل | نرم‌افزار رمزگذاری | Enforcement Case Tracking System ENFORCE | Facebook | نرم‌افزار فایروال | نرم‌افزار فلوچارت | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Google | نرم‌افزار Google Cloud | Google Earth Pro | نرم‌افزار ساخت گرافیک | Hypertext markup language HTML | IBM i2 Analyst's Notebook | JavaScript | LexisNexis | نرم‌افزار تحلیل پیوند | LinkedIn | Linux | McAfee | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Myspace | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Java | Oracle PeopleSoft | Palantir Intelligence | نرم‌افزار بهبود عکس | Python | R | Refugee, Asylum and Parole System RAPS | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار SAP | SAS | Snort | Splunk Enterprise | نرم‌افزار تحلیل آماری | زبان پرس‌و‌جوی ساختاریافته SQL | Student and Exchange Visitor Information System SEVIS | Tableau | نرم‌افزار تحلیل تلفن | نرم‌افزار سوابق تلفنی | TensorFlow | Teradata Database | نرم‌افزار متن‌کاوی | Thomson Reuters CLEAR | نرم‌افزار خط زمانی | Treasury Enforcement Communications System TECS | UNIX | Veritas NetBackup | نرم‌افزار مرورگر وب | Wireshark</t>
+          <t>Amazon Simple Storage Service S3 | نرم‌افزار Amazon Web Services AWS | Apache Hadoop | Apache Hive | Apache Kafka | Apache Pig | Apache Spark | Arrival Departure Information System ADIS | Automated Targeting System ATS | Bing | Biometric Storage System BSS | C++ | نرم‌افزار چت‌بات | Computer Linked Application Information Management System CLAIMS | Consular Consolidated Database CCD | نرم‌افزار تجسم داده | Django | نرم‌افزار ESRI ArcGIS | ESRI ArcView | نرم‌افزار ایمیل | نرم‌افزار رمزگذاری | Enforcement Case Tracking System ENFORCE | Facebook | نرم‌افزار فایروال | نرم‌افزار فلوچارت | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Google | نرم‌افزار Google Cloud | Google Earth Pro | نرم‌افزار ایجاد گرافیک | زبان نشانه‌گذاری ابرمتن HTML | IBM i2 Analyst's Notebook | JavaScript | LexisNexis | نرم‌افزار تحلیل پیوند | LinkedIn | Linux | McAfee | Microsoft Access | نرم‌افزار Microsoft Azure | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Word | Myspace | پایگاه داده مرکز ملی اطلاعات جرم (NCIC) | نرم‌افزار امنیت سایبری NortonLifeLock | Oracle Business Intelligence Enterprise Edition | Oracle Java | Oracle PeopleSoft | Palantir Intelligence | نرم‌افزار بهبود عکس | Python | R | Refugee, Asylum and Parole System RAPS | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار SAP | SAS | Snort | Splunk Enterprise | نرم‌افزار تحلیل آماری | زبان پرس‌وجوی ساختاریافته SQL | سیستم اطلاعات دانشجویان و بازدیدکنندگان مبادله‌ای SEVIS | Tableau | نرم‌افزار تحلیل تلفن | نرم‌افزار سوابق تلفنی | TensorFlow | Teradata Database | نرم‌افزار داده‌کاوی متن | Thomson Reuters CLEAR | نرم‌افزار خط زمانی | Treasury Enforcement Communications System TECS | UNIX | Veritas NetBackup | نرم‌افزار مرورگر وب | Wireshark</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | قانون و دولت | امنیت و ایمنی عمومی | رایانه‌ها و الکترونیک | اداری | ارتباطات و رسانه | خدمات مشتریان و پرسنل | مخابرات</t>
+          <t>زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | خدمات مشتری و شخصی | مخابرات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | بینایی نزدیک | انعطاف‌پذیری مقوله‌ای | روان بودن ایده‌ها | اصالت | بینایی دور | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | بینایی دور | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | داخل ساختمان، کنترل محیطی | مکالمات تلفنی | صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره به چهره با افراد و درون تیم‌ها | اهمیت دقیق یا منظم بودن | تماس با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | ارتباط با دیگران | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار وظایف یکسان | نامه‌ها و یادداشت‌های کتبی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیلگران هوش تجاری | دانشمندان داده | کارآگاهان و بازرسان جنایی | تحلیلگران جرم‌شناسی دیجیتال | متخصصان ریسک مالی | تکنسین‌های علوم جنایی | ارزیابان، بازرسان و تحلیلگران تقلب | افسران نظارت بر قمار و بازرسان قمار | تکنسین‌های اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیلگران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیلگران مدیریت | تست‌کنندگان نفوذ | افسران شناسایی و سوابق پلیس | کارآگاهان و بازرسان خصوصی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیت | دستیاران پژوهشی علوم اجتماعی | دستیاران آماری</t>
+          <t>تحلیلگران هوش تجاری | دانشمندان داده | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌شناسی دیجیتال | متخصصان ریسک مالی | تکنسین‌های علوم قانونی | بازرسان، محققان و تحلیلگران کلاهبرداری | ماموران نظارت بر قمار و بازرسان قمار | فن‌آوران اطلاعات سلامت و ثبت‌کنندگان پزشکی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت | کارشناسان آزمون نفوذ | افسران شناسایی و سوابق پلیس | کارآگاهان و بازرسان خصوصی | متخصصان پیشگیری از خسارت خرده‌فروشی | متخصصان مدیریت امنیت | مدیران امنیتی | دستیاران تحقیقات علوم اجتماعی | دستیاران آماری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0054_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0054_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | امور اداری و منابع انسانی | حقوق و امور حکومتی | زبان انگلیسی | امور دفتری و اداری | آموزش و تدریس | رایانه و الکترونیک | روان‌شناسی | مخابرات و ارتباطات | مهندسی و فناوری</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | خدمات مشتری و شخصی | پرسنل و منابع انسانی | قانون و دولت | زبان انگلیسی | اداری | آموزش و پرورش | رایانه و الکترونیک | روان‌شناسی | مخابرات | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | دید نزدیک | دید دور | تشخیص گفتار | استدلال قیاسی | درک کتبی | بیان کتبی | انعطاف‌پذیری در بستار | وضوح گفتار | مرتب‌سازی اطلاعات | توجه انتخابی | سرعت در بستار | سرعت ادراک | روان‌سازی ایده‌ها | انعطاف‌پذیری طبقه‌بندی</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال استقرایی | بینایی نزدیک | بینایی دور | تشخیص گفتار | استدلال قیاسی | درک کتبی | بیان کتبی | انعطاف‌پذیری بستار | وضوح گفتار | ترتیب‌دهی اطلاعات | توجه انتخابی | سرعت بستار | سرعت ادراکی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مدیران خدمات اداری | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول کارکنان تفریحی و سرگرمی، به‌جز خدمات قمار | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | سرپرستان رده‌اول کمک‌کارگران، کارگران ساده و جابه‌جا‌کنندگان دستی کالا | سرپرستان رده‌اول کارکنان خدمات و نظافت اماکن | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان امور دفتری و پشتیبانی اداری | سرپرستان رده‌اول مهمانداران و مهمان‌پذیران مسافری | سرپرستان رده‌اول کارکنان خدمات فردی | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان تولید و بهره‌برداری | مأموران گشت پلیس و کلانتری | کارشناسان پیشگیری از سرقت و کسری کالا در فروشگاه | نگهبانان و مأموران حراست | کارشناسان تخصصی مدیریت حراست | مدیران حراست و انتظامات | مأموران پلیس راه‌آهن و پایانه‌های مسافربری</t>
+          <t>مدیران خدمات اداری و پشتیبانی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول کارکنان مراکز تفریحی و سرگرمی، به‌جز بازی‌های شرط‌بندی | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول کارگران ساده و جابه‌جاکنندگان دستی بار | سرپرستان رده اول کارگران خدمات و نظافت ساختمان | سرپرستان رده‌اول اپراتورهای ماشین‌آلات و وسایل نقلیه جابه‌جایی بار | سرپرستان رده‌اول مکانیک‌ها، نصابان و تعمیرکاران | سرپرستان رده‌اول فروشندگان عمده‌فروشی و غیرخرده‌فروشی | سرپرستان رده‌اول کارکنان اداری و پشتیبانی | سرپرستان رده‌اول مهمانداران و خدمه مسافری | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده اول کارگران تولید و عملیات | ماموران گشت پلیس و کلانتری | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | حقوق و امور حکومتی | زبان انگلیسی | امور اداری و منابع انسانی | آموزش و تدریس | روان‌شناسی | رایانه و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | مدیریت و اداره | خدمات مشتری و شخصی | قانون و دولت | زبان انگلیسی | پرسنل و منابع انسانی | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری طبقه‌بندی | روان‌سازی ایده‌ها | ابتکار و اصالت | توجه انتخابی | اشتراک زمانی | تجسم فضایی | توانایی به‌خاطرسپاری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>سرپرستان رده‌اول کارکنان حراست و انتظامات | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | نگهبانان و مأموران حراست | کارشناسان پیشگیری از سرقت و کسری کالا در فروشگاه | مأموران نظارت و بازرسی مراکز قمار | کارآگاهان خصوصی و بازرسان | مأموران بازرسی و غربالگری امنیت حمل‌ونقل | مأموران زندان و بازداشتگاه | مأموران گشت پلیس و کلانتری | کارآگاهان و بازرسان جنایی | سایر کارکنان خدمات حفاظتی | مدیران حراست و انتظامات | مدیران مدیریت بحران و شرایط اضطراری | کارشناسان انطباق با قوانین و مقررات | کارشناسان بهداشت حرفه‌ای و ایمنی کار | مدیران پیشگیری از خسارت و سرقت | مدیران ارشد اجرایی و عملیاتی | کارشناسان تخصصی مدیریت حراست</t>
+          <t>سرپرستان رده‌اول کارکنان حراست و انتظامات | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | نگهبانان و ماموران حراست | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | کارآگاهان و بازرسان خصوصی | ماموران بازرسی و کنترل امنیتی حمل‌ونقل | مأموران زندان و بازداشتگاه | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان جنایی | سایر شاغلین خدمات حفاظتی و انتظامی | مدیران حراست و انتظامات | مدیران مدیریت بحران و پدافند غیرعامل | کارشناسان پایش انطباق و بازرسی مقرراتی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | مدیران پیشگیری از اتلاف منابع و صیانت از دارایی‌ها | مدیران کل و مدیران عملیات | کارشناسان مدیریت حراست و امنیت فیزیکی</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | شنیدن فعال | سخن گفتن | یادگیری فعال | نظارت | درک مطلب</t>
+          <t>تفکر انتقادی | گوش دادن فعال | سخن گفتن | یادگیری فعال | نظارت | درک مطلب</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | آموزش و تدریس | ساختمان و سازه | زبان انگلیسی | مکانیک | پزشکی و دندان‌پزشکی | مخابرات و ارتباطات | مدیریت و امور اداری | ترابری و حمل‌ونقل | حقوق و امور حکومتی | شیمی | روان‌شناسی | ریاضیات</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | آموزش و پرورش | ساختمان و ساخت‌وساز | زبان انگلیسی | مکانیک | پزشکی و دندان‌پزشکی | مخابرات | مدیریت و اداره | حمل و نقل | قانون و دولت | شیمی | روان‌شناسی | ریاضیات</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | ثبات دست و بازو | قدرت ایستا | دید دور | استقامت بدنی | استدلال استقرایی | دید نزدیک | وضوح گفتار | دقت در کنترل حرکت | هماهنگی چنداندامی | انعطاف‌پذیری در بستار | مرتب‌سازی اطلاعات | قدرت تنه | قدرت پویا | زمان واکنش | چابکی دستی | تشخیص گفتار | توجه شنیداری | سرعت ادراک | انعطاف‌پذیری دامنه حرکت | درک کتبی | جهت‌یابی فضایی | تجسم فضایی | درک عمق | تشخیص رنگ | قدرت انفجاری | توجه انتخابی | سرعت در بستار | انعطاف‌پذیری طبقه‌بندی | هماهنگی عمومی بدن | بیان کتبی | تعادل عمومی بدن | جهت‌گیری واکنش | چابکی انگشتان</t>
+          <t>حساسیت به مسئله | درک شفاهی | بیان شفاهی | استدلال قیاسی | ثبات دست و بازو | قدرت ایستا | بینایی دور | استقامت | استدلال استقرایی | بینایی نزدیک | وضوح گفتار | دقت کنترل | هماهنگی چند عضو | انعطاف‌پذیری بستار | ترتیب‌دهی اطلاعات | قدرت تنه | قدرت پویا | زمان عکس‌العمل | مهارت دستی | تشخیص گفتار | توجه شنیداری | سرعت ادراکی | انعطاف‌پذیری دامنه حرکت | درک کتبی | جهت‌گیری فضایی | تجسم | درک عمق | تشخیص رنگ بصری | قدرت انفجاری | توجه انتخابی | سرعت بستار | انعطاف‌پذیری دسته‌بندی | هماهنگی کلی بدن | بیان کتبی | تعادل کلی بدن | جهت‌گیری پاسخ | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌های نصب و تعمیر خطوط انتقال برق | مدیران مدیریت بحران و شرایط اضطراری | تکنسین‌های فوریت‌های پزشکی | بازرسان و کارشناسان بررسی علل حریق | مهندسان ایمنی و حفاظت در برابر حریق | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | بازرسان و کارشناسان پیشگیری از حریق جنگل | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران حفاظت از جنگل و منابع طبیعی | کارگران جمع‌آوری و دفع پسماندهای خطرناک | مهندسان ایمنی و بهداشت، به‌جز مهندسان و بازرسان ایمنی معدن | نجات‌غریق‌ها، گشت‌های پیست اسکی و سایر امدادگران اماکن تفریحی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | امدادگران و تکنسین‌های ارشد فوریت‌های پزشکی | ملوانان و روغن‌کاران موتورخانه شناور | نگهبانان و مأموران حراست | مهندسان فنی کشتی | تکنسین‌های موتورخانه و اپراتورهای دیگ بخار</t>
+          <t>رانندگان و خدمه آمبولانس، به‌جز تکنسین‌های فوریت‌های پزشکی | تکنسین‌ها و سیم‌بانان خطوط انتقال و توزیع برق | مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های فوریت‌های پزشکی | بازرسان و کارشناسان بررسی علل حریق | مهندسان پیشگیری و حفاظت از حریق | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | بازرسان و کارشناسان پیشگیری از حریق جنگل | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارگران امحا و پاک‌سازی مواد خطرناک | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | امدادگران و تکنسین‌های اورژانس (پارامدیک‌ها) | ملوانان و روغن‌کاران شناورهای دریایی | نگهبانان و ماموران حراست | مهندسان فنی کشتی | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نگارش | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>گوش دادن فعال | نگارش | سخن گفتن | تفکر انتقادی | درک مطلب | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | خدمات مشتریان و خدمات فردی | ساختمان و سازه | حقوق و امور حکومتی | آموزش و تدریس | زبان انگلیسی | مدیریت و امور اداری</t>
+          <t>ایمنی و امنیت عمومی | خدمات مشتری و شخصی | ساختمان و ساخت‌وساز | قانون و دولت | آموزش و پرورش | زبان انگلیسی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | انعطاف‌پذیری در بستار | انعطاف‌پذیری طبقه‌بندی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | روان‌سازی ایده‌ها | تشخیص رنگ | دید دور | ابتکار و اصالت</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان کتبی | استدلال قیاسی | بیان شفاهی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | تشخیص گفتار | توجه انتخابی | روانی ایده‌ها | تشخیص رنگ بصری | بینایی دور | اصالت</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>بازرسان ایمنی هوانوردی | بازرسان ساختمان و سازه | مدیران مدیریت بحران و شرایط اضطراری | بازرسان انطباق زیست‌محیطی | تکنسین‌های حفاظت و علوم محیط زیست، از جمله بهداشت | مهندسان ایمنی و حفاظت در برابر حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | سرپرستان رده‌اول کارکنان حراست و انتظامات | بازرسان و کارشناسان پیشگیری از حریق جنگل | بازرسان و مأموران تحقیق اموال دولتی | مهندسان ایمنی و بهداشت، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | نگهبانان و مأموران حراست | کارشناسان تخصصی مدیریت حراست | مدیران حراست و انتظامات | نصابان سیستم‌های اعلام و اطفای حریق و دزدگیر | مأموران پلیس راه‌آهن و پایانه‌های مسافربری | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به‌جز هوانوردی</t>
+          <t>بازرسان هوانوردی و فرودگاهی | بازرسان ساخت‌وساز و ساختمان | مدیران مدیریت بحران و پدافند غیرعامل | بازرسان رعایت ضوابط زیست‌محیطی | تکنسین‌های علوم و بهداشت محیط زیست | مهندسان پیشگیری و حفاظت از حریق | آتش‌نشانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول کارکنان حراست و انتظامات | بازرسان و کارشناسان پیشگیری از حریق جنگل | بازرسان و ممیزان اموال دولتی | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | نگهبانان و ماموران حراست | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | نصاب سیستم‌های اعلام سرقت و حریق | پلیس ترانزیت و راه‌آهن | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | شنیدن فعال | نظارت | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
+          <t>تفکر انتقادی | سخن گفتن | گوش دادن فعال | نظارت | راهبردهای یادگیری | درک مطلب | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | امور اداری و منابع انسانی | ایمنی و امنیت عمومی | حقوق و امور حکومتی | رایانه و الکترونیک | زبان انگلیسی | ترابری و حمل‌ونقل | امور دفتری و اداری | مکانیک | ارتباطات و رسانه | جغرافیا</t>
+          <t>مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | پرسنل و منابع انسانی | ایمنی و امنیت عمومی | قانون و دولت | رایانه و الکترونیک | زبان انگلیسی | حمل و نقل | اداری | مکانیک | ارتباطات و رسانه | جغرافیا</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | دید نزدیک | درک کتبی | دید دور | انعطاف‌پذیری در بستار | استدلال استقرایی | وضوح گفتار | سرعت ادراک | بیان کتبی | سرعت در بستار | مرتب‌سازی اطلاعات | تشخیص گفتار | درک عمق | هماهنگی چنداندامی | توجه انتخابی | انعطاف‌پذیری طبقه‌بندی | ابتکار و اصالت</t>
+          <t>بیان شفاهی | حساسیت به مسئله | درک شفاهی | استدلال قیاسی | بینایی نزدیک | درک کتبی | بینایی دور | انعطاف‌پذیری بستار | استدلال استقرایی | وضوح گفتار | سرعت ادراکی | بیان کتبی | سرعت بستار | ترتیب‌دهی اطلاعات | تشخیص گفتار | درک عمق | هماهنگی چند عضو | توجه انتخابی | انعطاف‌پذیری دسته‌بندی | اصالت</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مدیران مدیریت بحران و شرایط اضطراری | تکنسین‌های حفاظت و علوم محیط زیست، از جمله بهداشت | دانشمندان و کارشناسان محیط زیست، از جمله بهداشت | بازرسان و کارشناسان بررسی علل حریق | مهندسان ایمنی و حفاظت در برابر حریق | آتش‌نشانان | سرپرستان رده‌اول کارکنان کشاورزی، صیادی و جنگل‌داری | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران حفاظت از جنگل و منابع طبیعی | جنگل‌داران و کارشناسان جنگل | مهندسان ایمنی و بهداشت، به‌جز مهندسان و بازرسان ایمنی معدن | نجات‌غریق‌ها، گشت‌های پیست اسکی و سایر امدادگران اماکن تفریحی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | مأموران دریافت پیام‌های فوریت و امنیت عمومی | مدیران مراتع و آبخیزداری | نگهبانان و مأموران حراست | مأموران پلیس راه‌آهن و پایانه‌های مسافربری | بازرسان وسایل نقلیه، تجهیزات و سیستم‌های حمل‌ونقل، به‌جز هوانوردی</t>
+          <t>مدیران مدیریت بحران و پدافند غیرعامل | تکنسین‌های علوم و بهداشت محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بازرسان و کارشناسان بررسی علل حریق | مهندسان پیشگیری و حفاظت از حریق | آتش‌نشانان | سرپرستان رده‌اول کارگران کشاورزی، شیلات و جنگل‌داری | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | کاردان‌ها و تکنسین‌های جنگل‌داری و حفاظت منابع طبیعی | کارگران جنگل‌داری و حفاظت از منابع طبیعی | کارشناسان جنگل‌داری و جنگل‌بانان | مهندسان بهداشت و ایمنی، به‌جز مهندسان و بازرسان ایمنی معدن | ناجیان غریق، گشت اسکی و سایر مشاغل خدمات حفاظتی و امدادی تفریحی | کارشناسان بهداشت حرفه‌ای و ایمنی کار | کاردان‌ها و تکنسین‌های بهداشت حرفه‌ای و ایمنی کار | اپراتورهای فوریت‌های پلیسی و امدادی | مدیران و کارشناسان مدیریت مراتع | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن | بازرسان سامانه‌ها، تجهیزات و وسایل نقلیه ترابری (به‌جز هوانوردی)</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | نظارت | شنیدن فعال | تفکر انتقادی</t>
+          <t>سخن گفتن | نظارت | گوش دادن فعال | تفکر انتقادی</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و امور حکومتی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان شفاهی | توجه انتخابی | وضوح گفتار | درک شفاهی | تشخیص گفتار | دید نزدیک | استدلال قیاسی | قدرت تنه | قدرت ایستا | مرتب‌سازی اطلاعات | استدلال استقرایی | درک کتبی</t>
+          <t>حساسیت به مسئله | بیان شفاهی | توجه انتخابی | وضوح گفتار | درک شفاهی | تشخیص گفتار | بینایی نزدیک | استدلال قیاسی | قدرت تنه | قدرت ایستا | ترتیب‌دهی اطلاعات | استدلال استقرایی | درک کتبی</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، مراجع رسیدگی و داوران | داوران، میانجی‌گران و صلح‌یاران | مأموران پزشک قانونی و ثبت فوت | مأموران زندان و بازداشتگاه | تندنویسان دادگاه و پیاده‌سازان هم‌زمان صورت‌جلسات | کارمندان دادگاه، شهرداری و صدور مجوزها | مأموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | قضات، دادرسان و مأموران دادرسی دادگاه | کارآموزان و دستیاران حقوقی قضات | وکلا | مسئولان دفاتر و کارشناسان اداری امور حقوقی | مأموران گشت پلیس و کلانتری | کارآگاهان خصوصی و بازرسان | مأموران آزادی مشروط و مددکاران اقدامات تأمینی و تربیتی | نگهبانان و مأموران حراست | مأموران پلیس راه‌آهن و پایانه‌های مسافربری</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | داوران، میانجی‌گران و صلح‌یاران | پزشکان قانونی و بازرسان مرگ مشکوک | مأموران زندان و بازداشتگاه | تندنویسان و ثبت‌کنندگان هم‌زمان صورت‌جلسات | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | ماموران گمرک و حفاظت مرزی | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | قضات دادگاه و دادیاران | کارشناسان پژوهش و تحریر قضایی | وکلا | منشی‌ها و دستیاران اداری دفاتر حقوقی | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مددکاران قضایی و متخصصان اصلاح و تربیت | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
+          <t>گوش دادن فعال | نظارت | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | زبان انگلیسی | حقوق و امور حکومتی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | رایانه و الکترونیک | روان‌شناسی | آموزش و تدریس | امور دفتری و اداری | مخابرات و ارتباطات</t>
+          <t>ایمنی و امنیت عمومی | زبان انگلیسی | قانون و دولت | خدمات مشتری و شخصی | مدیریت و اداره | رایانه و الکترونیک | روان‌شناسی | آموزش و پرورش | اداری | مخابرات</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | دید نزدیک | تشخیص گفتار | توجه انتخابی | درک کتبی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در بستار | دید دور | استقامت بدنی | بیان کتبی | قدرت تنه | قدرت پویا | قدرت انفجاری | قدرت ایستا | زمان واکنش | هماهنگی چنداندامی | چابکی دستی | ثبات دست و بازو | اشتراک زمانی | سرعت ادراک | توجه شنیداری | انعطاف‌پذیری دامنه حرکت</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | توجه انتخابی | درک کتبی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری بستار | بینایی دور | استقامت | بیان کتبی | قدرت تنه | قدرت پویا | قدرت انفجاری | قدرت ایستا | زمان عکس‌العمل | هماهنگی چند عضو | مهارت دستی | ثبات دست و بازو | تقسیم توجه | سرعت ادراکی | توجه شنیداری | انعطاف‌پذیری دامنه حرکت</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مأموران انتظامات و حفاظت دادگاه | مددکاران اجتماعی کودک، خانواده و مدرسه | مأموران پزشک قانونی و ثبت فوت | کارمندان دادگاه، شهرداری و صدور مجوزها | مدرسان علوم قضایی و انتظامی، آموزش عالی | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول کارکنان آتش‌نشانی و پیشگیری از حریق | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران خدمات بهداشتی و درمانی | مأموران گشت پلیس و کلانتری | کارآگاهان خصوصی و بازرسان | مأموران آزادی مشروط و مددکاران اقدامات تأمینی و تربیتی | بهیاران و دستیاران روان‌پزشکی | مشاوران توان‌بخشی | مشاوران خوابگاه‌ها و اقامتگاه‌ها | نگهبانان و مأموران حراست | مدیران خدمات اجتماعی و خدمات رفاهی | مأموران پلیس راه‌آهن و پایانه‌های مسافربری</t>
+          <t>مأموران انتظامات و حفاظت دادگاه | مددکاران اجتماعی کودک، خانواده و مدرسه | پزشکان قانونی و بازرسان مرگ مشکوک | کارمندان و متصدیان امور دفتری دادگاه‌ها، شهرداری‌ها و مراجع صدور پروانه | مدرسان حقوق جزا، جرم‌شناسی و علوم انتظامی در دانشگاه‌ها و مراکز آموزش عالی | کارآگاهان و بازرسان جنایی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول آتش‌نشانی و خدمات ایمنی و پیشگیری | سرپرستان رده‌اول پلیس و کارآگاهان | سرپرستان رده‌اول کارکنان حراست و انتظامات | مدیران خدمات درمانی و بهداشتی | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مددکاران قضایی و متخصصان اصلاح و تربیت | کمک‌یاران بخش روان‌پزشکی | مشاوران توانبخشی | سرپرستان و مشاوران خوابگاه | نگهبانان و ماموران حراست | مدیران خدمات اجتماعی و خدمات مردمی | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت</t>
+          <t>گوش دادن فعال | سخن گفتن | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>حقوق و امور حکومتی | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتریان و خدمات فردی | روان‌شناسی | رایانه و الکترونیک | آموزش و تدریس | امور دفتری و اداری | مدیریت و امور اداری | ارتباطات و رسانه | جامعه‌شناسی و مردم‌شناسی</t>
+          <t>قانون و دولت | ایمنی و امنیت عمومی | زبان انگلیسی | خدمات مشتری و شخصی | روان‌شناسی | رایانه و الکترونیک | آموزش و پرورش | اداری | مدیریت و اداره | ارتباطات و رسانه | جامعه‌شناسی و انسان‌شناسی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | بیان کتبی | انعطاف‌پذیری طبقه‌بندی | انعطاف‌پذیری در بستار | دید دور | سرعت در بستار | روان‌سازی ایده‌ها | سرعت ادراک | توجه انتخابی | اشتراک زمانی | ابتکار و اصالت</t>
+          <t>درک شفاهی | استدلال استقرایی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | بیان کتبی | انعطاف‌پذیری دسته‌بندی | انعطاف‌پذیری بستار | بینایی دور | سرعت بستار | روانی ایده‌ها | سرعت ادراکی | توجه انتخابی | تقسیم توجه | اصالت</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>قضات دادگاه‌های اداری، مراجع رسیدگی و داوران | مأموران انتظامات و حفاظت دادگاه | کارشناسان انطباق با قوانین و مقررات | مأموران پزشک قانونی و ثبت فوت | مأموران زندان و بازداشتگاه | مأموران گمرک و حفاظت مرزی | سرپرستان رده‌اول مأموران زندان | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | تکنسین‌های علوم جنایی و آزمایشگاه تشخیص هویت | کارشناسان، بازرسان و تحلیل‌گران بررسی تقلب و کلاهبرداری | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارآموزان و دستیاران حقوقی قضات | وکلا | کارشناسان تشخیص هویت و ثبت سوابق پلیس | مأموران گشت پلیس و کلانتری | کارآگاهان خصوصی و بازرسان | مأموران آزادی مشروط و مددکاران اقدامات تأمینی و تربیتی | کارشناسان پیشگیری از سرقت و کسری کالا در فروشگاه | نگهبانان و مأموران حراست | مأموران پلیس راه‌آهن و پایانه‌های مسافربری</t>
+          <t>قضات دادگاه‌های اداری، دادرسان و مأموران استماع | مأموران انتظامات و حفاظت دادگاه | کارشناسان پایش انطباق و بازرسی مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | مأموران زندان و بازداشتگاه | ماموران گمرک و حفاظت مرزی | سرپرستان رده‌اول ماموران مراقبت پرواز و زندان‌بانان | سرپرستان رده‌اول پلیس و کارآگاهان | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کارشناسان پژوهش و تحریر قضایی | وکلا | کارشناسان تشخیص هویت و ثبت سوابق پلیس | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | مددکاران قضایی و متخصصان اصلاح و تربیت | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | نگهبانان و ماموران حراست | پلیس ترانزیت و راه‌آهن</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>شنیدن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
+          <t>گوش دادن فعال | سخن گفتن | درک مطلب | تفکر انتقادی | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حقوق و امور حکومتی | امور دفتری و اداری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتریان و خدمات فردی | آموزش و تدریس</t>
+          <t>قانون و دولت | اداری | زبان انگلیسی | ایمنی و امنیت عمومی | رایانه و الکترونیک | خدمات مشتری و شخصی | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در بستار | حساسیت به مسئله | انعطاف‌پذیری طبقه‌بندی | ثبات دست و بازو | روان‌سازی ایده‌ها | توجه انتخابی | سرعت ادراک | تشخیص رنگ | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | بیان کتبی | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | حساسیت به مسئله | انعطاف‌پذیری دسته‌بندی | ثبات دست و بازو | روانی ایده‌ها | توجه انتخابی | سرعت ادراکی | تشخیص رنگ بصری | بینایی دور</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>هماهنگ‌کنندگان پژوهش‌های بالینی | کارشناسان انطباق با قوانین و مقررات | مأموران پزشک قانونی و ثبت فوت | کارآگاهان و بازرسان جنایی | تحلیل‌گران فارنزیک دیجیتال و جرایم سایبری | بازرسان انطباق زیست‌محیطی | تکنسین‌های حفاظت و علوم محیط زیست، از جمله بهداشت | کارمندان بایگانی و ثبت اسناد | سرپرستان رده‌اول مأموران پلیس و کارآگاهان | تکنسین‌های علوم جنایی و آزمایشگاه تشخیص هویت | کارشناسان، بازرسان و تحلیل‌گران بررسی تقلب و کلاهبرداری | بازرسان و مأموران تحقیق اموال دولتی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | تکنسین‌های آزمایشگاه پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | دستیاران حقوقی و پژوهشگران وکالت | مأموران گشت پلیس و کلانتری | کارآگاهان خصوصی و بازرسان | دستیاران پژوهشی علوم اجتماعی | دستیاران آمار و اطلاعات</t>
+          <t>هماهنگ‌کنندگان کارآزمایی‌های بالینی | کارشناسان پایش انطباق و بازرسی مقرراتی | پزشکان قانونی و بازرسان مرگ مشکوک | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | بازرسان رعایت ضوابط زیست‌محیطی | تکنسین‌های علوم و بهداشت محیط زیست | متصدیان بایگانی و اسناد | سرپرستان رده‌اول پلیس و کارآگاهان | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | بازرسان و ممیزان اموال دولتی | تحلیل‌گران داده‌ها و اطلاعات امنیتی | کاردان‌های آزمایشگاه‌های پزشکی و بالینی | کارشناسان علوم آزمایشگاهی بالینی | کارشناسان و دستیاران امور حقوقی | ماموران گشت پلیس و کلانتری | کارآگاهان و بازرسان خصوصی | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | گوش دادن فعال | سخن گفتن | نگارش | تفکر انتقادی | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و امور حکومتی | ایمنی و امنیت عمومی | رایانه و الکترونیک | امور دفتری و اداری | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | مخابرات و ارتباطات</t>
+          <t>زبان انگلیسی | قانون و دولت | ایمنی و امنیت عمومی | رایانه و الکترونیک | اداری | ارتباطات و رسانه | خدمات مشتری و شخصی | مخابرات</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری در بستار | دید نزدیک | انعطاف‌پذیری طبقه‌بندی | روان‌سازی ایده‌ها | ابتکار و اصالت | دید دور | توجه انتخابی | سرعت ادراک | سرعت در بستار</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | حساسیت به مسئله | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | انعطاف‌پذیری بستار | بینایی نزدیک | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | بینایی دور | توجه انتخابی | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تحلیل‌گران هوش تجاری BI | دانشمندان علم داده | کارآگاهان و بازرسان جنایی | تحلیل‌گران فارنزیک دیجیتال و جرایم سایبری | کارشناسان تحلیل ریسک مالی | تکنسین‌های علوم جنایی و آزمایشگاه تشخیص هویت | کارشناسان، بازرسان و تحلیل‌گران بررسی تقلب و کلاهبرداری | مأموران نظارت و بازرسی مراکز قمار | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | تحلیل‌گران مدیریت و فرایندها | کارشناسان آزمون نفوذپذیری و تست نفوذ | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارآگاهان خصوصی و بازرسان | کارشناسان پیشگیری از سرقت و کسری کالا در فروشگاه | کارشناسان تخصصی مدیریت حراست | مدیران حراست و انتظامات | دستیاران پژوهشی علوم اجتماعی | دستیاران آمار و اطلاعات</t>
+          <t>تحلیل‌گران هوش تجاری | دانشمندان داده | کارآگاهان و بازرسان جنایی | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | کارشناسان ریسک مالی | کاردان‌ها و تکنسین‌های علوم آزمایشگاهی و کشف علمی جرایم | کارشناسان بازرسی، کشف و تحلیل تقلب | ماموران و بازرسان نظارت تصویری و پایش اماکن سرگرمی و بازی | کارشناسان فناوری اطلاعات سلامت و ثبت داده‌های پزشکی | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | کارشناسان تحلیل مدیریت و روش‌ها | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان تشخیص هویت و ثبت سوابق پلیس | کارآگاهان و بازرسان خصوصی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | کارشناسان مدیریت حراست و امنیت فیزیکی | مدیران حراست و انتظامات | کمک‌کارشناسان و دستیاران پژوهشی علوم اجتماعی | دستیاران و تکنسین‌های آمار</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
